--- a/artfynd/A 43401-2019 artfynd.xlsx
+++ b/artfynd/A 43401-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43401-2019 artfynd.xlsx
+++ b/artfynd/A 43401-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61604647</v>
+        <v>89328122</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
+        <v>93158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Prästtorp, NV om, Srm</t>
+          <t>250 m N-NÖ Norrtorp, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576428.6548334835</v>
+        <v>576115.8020014314</v>
       </c>
       <c r="R2" t="n">
-        <v>6567699.124149692</v>
+        <v>6567681.079871805</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +745,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-09-01</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-01</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -781,30 +772,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Berg, mossigt</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89328122</v>
+        <v>89368153</v>
       </c>
       <c r="B3" t="n">
-        <v>93158</v>
+        <v>93235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +803,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>250 m N-NÖ Norrtorp, Srm</t>
+          <t>250 m N-NÖ Norrtorp (Bv2020_S42), Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576115.8020014314</v>
+        <v>576155.1255304982</v>
       </c>
       <c r="R3" t="n">
-        <v>6567681.079871805</v>
+        <v>6567714.105654766</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,6 +869,11 @@
           <t>Näshulta</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Bv2020_S42</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2020-08-06</t>
@@ -898,6 +903,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Dikespåverkad, äldre gallringsskog av gran. I området finns gott om murkna, fuktiga stubbar.</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Klen (ca 10 cm grov) lövlåga (björk eller gråal) i kanten på äldre dike.</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -909,157 +933,7 @@
           <t>Jenny Andersson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>89368153</v>
-      </c>
-      <c r="B4" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>210</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Buxbaumia viridis</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>250 m N-NÖ Norrtorp (Bv2020_S42), Srm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>576155.1255304982</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6567714.105654766</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Näshulta</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Bv2020_S42</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2020-08-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2020-08-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Dikespåverkad, äldre gallringsskog av gran. I området finns gott om murkna, fuktiga stubbar.</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Klen (ca 10 cm grov) lövlåga (björk eller gråal) i kanten på äldre dike.</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
         </is>
